--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-18 10:42</t>
+    <t xml:space="preserve">2026-09-06 19:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
